--- a/3_CGE/Game_theory_2024/0_External_data/qxw_values.xlsx
+++ b/3_CGE/Game_theory_2024/0_External_data/qxw_values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\runGTAP375\Game_theory_2024\0_External_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F0BADA-A8EF-40F8-9F16-86BE32E84434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1B2C7E-C059-4AA3-8E53-411E0BD65C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10960" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{1BE1B400-F79A-4081-9485-F0F2366A7D5A}"/>
+    <workbookView xWindow="16690" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{1BE1B400-F79A-4081-9485-F0F2366A7D5A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Country</t>
   </si>
@@ -83,9 +83,6 @@
     <t xml:space="preserve">colombia   </t>
   </si>
   <si>
-    <t xml:space="preserve">angdrc     </t>
-  </si>
-  <si>
     <t xml:space="preserve">ghana      </t>
   </si>
   <si>
@@ -99,6 +96,12 @@
   </si>
   <si>
     <t xml:space="preserve">peru       </t>
+  </si>
+  <si>
+    <t>angola</t>
+  </si>
+  <si>
+    <t>drc</t>
   </si>
 </sst>
 </file>
@@ -454,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F83C31E-1F5F-495B-8648-E82BD436A23B}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -494,31 +497,31 @@
         <v>10</v>
       </c>
       <c r="B2" s="1">
-        <v>-1.1000000000000001</v>
+        <v>-1.6723376794962399</v>
       </c>
       <c r="C2" s="1">
-        <v>-1.43</v>
+        <v>-1.9196079004924875</v>
       </c>
       <c r="D2" s="1">
-        <v>-2.89</v>
+        <v>-2.7558985848572726</v>
       </c>
       <c r="E2" s="1">
-        <v>-1.89</v>
+        <v>-0.1604641310330728</v>
       </c>
       <c r="F2" s="1">
-        <v>-3.23</v>
+        <v>-4.1152896617819481</v>
       </c>
       <c r="G2" s="1">
-        <v>-0.5</v>
+        <v>-0.32415605702635442</v>
       </c>
       <c r="H2" s="1">
-        <v>-2.9</v>
+        <v>-5.2871023596143258</v>
       </c>
       <c r="I2" s="1">
-        <v>-1.32</v>
+        <v>-0.4551162969937726</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.61</v>
+        <v>-4.3082198150677886</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -526,28 +529,28 @@
         <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>-1.1599999999999999</v>
+        <v>-4.0246364451652639</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.62</v>
+        <v>-2.2178035992971914</v>
       </c>
       <c r="D3" s="1">
-        <v>-4.95</v>
+        <v>-10.442780191250822</v>
       </c>
       <c r="E3" s="1">
-        <v>-1.81</v>
+        <v>-3.0168753156801063</v>
       </c>
       <c r="F3" s="1">
-        <v>-5.12</v>
+        <v>-18.740877943436466</v>
       </c>
       <c r="G3" s="1">
-        <v>-0.46</v>
+        <v>-1.0677211323407854</v>
       </c>
       <c r="H3" s="1">
-        <v>-14.23</v>
+        <v>-41.491048826065843</v>
       </c>
       <c r="I3" s="1">
-        <v>-0.76</v>
+        <v>-1.5206394431597063</v>
       </c>
       <c r="J3" s="1">
         <v>0</v>
@@ -558,31 +561,31 @@
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>-0.6</v>
+        <v>-3.2592816165294627</v>
       </c>
       <c r="C4" s="1">
-        <v>-5.4</v>
+        <v>-10.33368572011617</v>
       </c>
       <c r="D4" s="1">
-        <v>-2.09</v>
+        <v>-22.394819271147433</v>
       </c>
       <c r="E4" s="1">
-        <v>-1.08</v>
+        <v>-3.5330811594172671</v>
       </c>
       <c r="F4" s="1">
-        <v>-1.08</v>
+        <v>-2.0125972621416643</v>
       </c>
       <c r="G4" s="1">
-        <v>-0.92</v>
+        <v>-4.4628622369061421</v>
       </c>
       <c r="H4" s="1">
-        <v>-2</v>
+        <v>-1.6687258339981561</v>
       </c>
       <c r="I4" s="1">
-        <v>-0.81</v>
+        <v>-2.7598774804851423</v>
       </c>
       <c r="J4" s="1">
-        <v>-0.93</v>
+        <v>-1.0050811425673827</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -590,31 +593,31 @@
         <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>-2.44</v>
+        <v>-12.649951689465617</v>
       </c>
       <c r="C5" s="1">
-        <v>-2.88</v>
+        <v>-2.576452136380186</v>
       </c>
       <c r="D5" s="1">
-        <v>-15.81</v>
+        <v>-28.273817766748337</v>
       </c>
       <c r="E5" s="1">
-        <v>-7.14</v>
+        <v>-11.385096173096438</v>
       </c>
       <c r="F5" s="1">
-        <v>-4.32</v>
+        <v>-13.405632030785759</v>
       </c>
       <c r="G5" s="1">
-        <v>-3.41</v>
+        <v>-8.534651666069939</v>
       </c>
       <c r="H5" s="1">
-        <v>-6.57</v>
+        <v>-36.361072353619136</v>
       </c>
       <c r="I5" s="1">
-        <v>-5.03</v>
+        <v>-5.1946086854736313</v>
       </c>
       <c r="J5" s="1">
-        <v>-4.13</v>
+        <v>-30.704496097842831</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -622,92 +625,92 @@
         <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>-2.83</v>
+        <v>-5.8083733799160093</v>
       </c>
       <c r="C6" s="1">
-        <v>-1.61</v>
+        <v>-1.8673556284186359</v>
       </c>
       <c r="D6" s="1">
-        <v>-5.34</v>
+        <v>-6.5249602147018653</v>
       </c>
       <c r="E6" s="1">
-        <v>-5.45</v>
+        <v>-4.8699812692597009</v>
       </c>
       <c r="F6" s="1">
-        <v>-7.91</v>
+        <v>-20.859493256001233</v>
       </c>
       <c r="G6" s="1">
-        <v>-2.54</v>
+        <v>-8.0426911288215255</v>
       </c>
       <c r="H6" s="1">
-        <v>-2.4</v>
+        <v>-4.1822389372623281</v>
       </c>
       <c r="I6" s="1">
-        <v>-5</v>
+        <v>-6.7710432008686903</v>
       </c>
       <c r="J6" s="1">
-        <v>-5.96</v>
+        <v>-26.209024554975635</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1">
-        <v>-0.83</v>
+        <v>-3.2592816165294627</v>
       </c>
       <c r="C7" s="1">
-        <v>-1.58</v>
+        <v>-10.33368572011617</v>
       </c>
       <c r="D7" s="1">
-        <v>-10.15</v>
+        <v>-22.394819271147433</v>
       </c>
       <c r="E7" s="1">
-        <v>-2.88</v>
+        <v>-3.5330811594172671</v>
       </c>
       <c r="F7" s="1">
-        <v>-1.47</v>
+        <v>-2.0125972621416643</v>
       </c>
       <c r="G7" s="1">
-        <v>-6.71</v>
+        <v>-4.4628622369061421</v>
       </c>
       <c r="H7" s="1">
-        <v>-0.85</v>
+        <v>-1.6687258339981561</v>
       </c>
       <c r="I7" s="1">
-        <v>-4.72</v>
+        <v>-2.7598774804851423</v>
       </c>
       <c r="J7" s="1">
-        <v>-0.67</v>
+        <v>-1.0050811425673827</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>-2.5499999999999998</v>
+        <v>-8.2228986546205558</v>
       </c>
       <c r="C8" s="1">
-        <v>-2.2400000000000002</v>
+        <v>-1.0104755651357047</v>
       </c>
       <c r="D8" s="1">
-        <v>-4.4800000000000004</v>
+        <v>-1.0635868807786328</v>
       </c>
       <c r="E8" s="1">
-        <v>-6.66</v>
+        <v>-8.9609572144490883</v>
       </c>
       <c r="F8" s="1">
-        <v>-6.2</v>
+        <v>-12.100729048226007</v>
       </c>
       <c r="G8" s="1">
-        <v>-6.51</v>
+        <v>-26.451775486787799</v>
       </c>
       <c r="H8" s="1">
-        <v>-9.19</v>
+        <v>-26.425974432654776</v>
       </c>
       <c r="I8" s="1">
-        <v>-6.19</v>
+        <v>-10.761599243689275</v>
       </c>
       <c r="J8" s="1">
         <v>0</v>
@@ -715,31 +718,31 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>-11.51</v>
+        <v>-7.5118698993463502</v>
       </c>
       <c r="C9" s="1">
-        <v>-6.97</v>
+        <v>-0.47971667978146237</v>
       </c>
       <c r="D9" s="1">
-        <v>-11.89</v>
+        <v>-2.577938250719841</v>
       </c>
       <c r="E9" s="1">
-        <v>-24.36</v>
+        <v>-25.059588584565812</v>
       </c>
       <c r="F9" s="1">
-        <v>-14.18</v>
+        <v>-7.283225884355188</v>
       </c>
       <c r="G9" s="1">
-        <v>-10.3</v>
+        <v>-11.480273866940198</v>
       </c>
       <c r="H9" s="1">
-        <v>-18.649999999999999</v>
+        <v>-15.610706231166374</v>
       </c>
       <c r="I9" s="1">
-        <v>-21.32</v>
+        <v>-11.508253303697305</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -747,31 +750,31 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>-25.53</v>
+        <v>-59.103001414794655</v>
       </c>
       <c r="C10" s="1">
-        <v>-0.8</v>
+        <v>-0.50691244239631339</v>
       </c>
       <c r="D10" s="1">
-        <v>-6.94</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>-0.91</v>
+        <v>-3.1762656932205888</v>
       </c>
       <c r="F10" s="1">
-        <v>-2.21</v>
+        <v>-8.5689544262329456</v>
       </c>
       <c r="G10" s="1">
-        <v>-1.95</v>
+        <v>-8.7256866096993964</v>
       </c>
       <c r="H10" s="1">
-        <v>-8.1199999999999992</v>
+        <v>-31.434657036442747</v>
       </c>
       <c r="I10" s="1">
-        <v>-4.28</v>
+        <v>-9.81412982052702</v>
       </c>
       <c r="J10" s="1">
         <v>0</v>
@@ -779,69 +782,113 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>-3.98</v>
+        <v>-6.640568143636469</v>
       </c>
       <c r="C11" s="1">
-        <v>-1.3</v>
+        <v>-0.40723966233655384</v>
       </c>
       <c r="D11" s="1">
-        <v>-19.22</v>
+        <v>-18.647303978264375</v>
       </c>
       <c r="E11" s="1">
-        <v>-6.48</v>
+        <v>-8.4442076582985504</v>
       </c>
       <c r="F11" s="1">
-        <v>-6.16</v>
+        <v>-9.9362432150602853</v>
       </c>
       <c r="G11" s="1">
-        <v>-18.21</v>
+        <v>-47.701335003384315</v>
       </c>
       <c r="H11" s="1">
-        <v>-15.87</v>
+        <v>-26.076203140711002</v>
       </c>
       <c r="I11" s="1">
-        <v>-4.1399999999999997</v>
+        <v>-3.7383898616248699</v>
       </c>
       <c r="J11" s="1">
-        <v>-5.46</v>
+        <v>-8.309618550856527</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>-4.45</v>
+        <v>-6.4571840254064758</v>
       </c>
       <c r="C12" s="1">
-        <v>-5.73</v>
+        <v>-4.6869779511358942</v>
       </c>
       <c r="D12" s="1">
-        <v>-8.1300000000000008</v>
+        <v>-2.4952562952907202</v>
       </c>
       <c r="E12" s="1">
-        <v>-13.7</v>
+        <v>-15.373617727978653</v>
       </c>
       <c r="F12" s="1">
-        <v>-23.93</v>
+        <v>-21.677612600318135</v>
       </c>
       <c r="G12" s="1">
-        <v>-4.9800000000000004</v>
+        <v>-5.3175607443009794</v>
       </c>
       <c r="H12" s="1">
-        <v>-23.75</v>
+        <v>-24.729064412469807</v>
       </c>
       <c r="I12" s="1">
-        <v>-7.48</v>
+        <v>-2.4873161832720427</v>
       </c>
       <c r="J12" s="1">
-        <v>-3.23</v>
+        <v>-2.979629864170882</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <v>-4.5842156854696148</v>
+      </c>
+      <c r="C13">
+        <v>-0.95145621289964843</v>
+      </c>
+      <c r="D13">
+        <v>-8.2336566557987538</v>
+      </c>
+      <c r="E13">
+        <v>-38.814775182315877</v>
+      </c>
+      <c r="F13">
+        <v>-33.417434428107569</v>
+      </c>
+      <c r="G13">
+        <v>-12.381410690553825</v>
+      </c>
+      <c r="H13">
+        <v>-48.24458570746237</v>
+      </c>
+      <c r="I13">
+        <v>-11.984357710892249</v>
+      </c>
+      <c r="J13">
+        <v>-23.353207910254277</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:J13">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>